--- a/output/stock_quant_scores/RIO_info.xlsx
+++ b/output/stock_quant_scores/RIO_info.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FP2"/>
+  <dimension ref="A1:FT2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1051,235 +1051,255 @@
       </c>
       <c r="DV1" s="1" t="inlineStr">
         <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DW1" s="1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DX1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketTime</t>
+        </is>
+      </c>
+      <c r="DY1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DZ1" s="1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="EA1" s="1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="EB1" s="1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="EC1" s="1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="ED1" s="1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="EE1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="EF1" s="1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="EG1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="EH1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="EI1" s="1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="EJ1" s="1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="EK1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="EL1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="EM1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="EN1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="EO1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="EP1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="EQ1" s="1" t="inlineStr">
+        <is>
+          <t>dividendDate</t>
+        </is>
+      </c>
+      <c r="ER1" s="1" t="inlineStr">
+        <is>
           <t>earningsTimestamp</t>
         </is>
       </c>
-      <c r="DW1" s="1" t="inlineStr">
+      <c r="ES1" s="1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="DX1" s="1" t="inlineStr">
+      <c r="ET1" s="1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="DY1" s="1" t="inlineStr">
+      <c r="EU1" s="1" t="inlineStr">
         <is>
           <t>earningsCallTimestampStart</t>
         </is>
       </c>
-      <c r="DZ1" s="1" t="inlineStr">
+      <c r="EV1" s="1" t="inlineStr">
         <is>
           <t>earningsCallTimestampEnd</t>
         </is>
       </c>
-      <c r="EA1" s="1" t="inlineStr">
+      <c r="EW1" s="1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="EB1" s="1" t="inlineStr">
+      <c r="EX1" s="1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="EC1" s="1" t="inlineStr">
+      <c r="EY1" s="1" t="inlineStr">
         <is>
           <t>epsForward</t>
         </is>
       </c>
-      <c r="ED1" s="1" t="inlineStr">
+      <c r="EZ1" s="1" t="inlineStr">
         <is>
           <t>epsCurrentYear</t>
         </is>
       </c>
-      <c r="EE1" s="1" t="inlineStr">
+      <c r="FA1" s="1" t="inlineStr">
         <is>
           <t>priceEpsCurrentYear</t>
         </is>
       </c>
-      <c r="EF1" s="1" t="inlineStr">
+      <c r="FB1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="FC1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="FD1" s="1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="FE1" s="1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="FF1" s="1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="FG1" s="1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="FH1" s="1" t="inlineStr">
+        <is>
+          <t>averageAnalystRating</t>
+        </is>
+      </c>
+      <c r="FI1" s="1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="FJ1" s="1" t="inlineStr">
         <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="EG1" s="1" t="inlineStr">
+      <c r="FK1" s="1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="EH1" s="1" t="inlineStr">
+      <c r="FL1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="FM1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketPrice</t>
+        </is>
+      </c>
+      <c r="FN1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketChange</t>
+        </is>
+      </c>
+      <c r="FO1" s="1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="EI1" s="1" t="inlineStr">
+      <c r="FP1" s="1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="EJ1" s="1" t="inlineStr">
+      <c r="FQ1" s="1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="EK1" s="1" t="inlineStr">
+      <c r="FR1" s="1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="EL1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="EM1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="EN1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EO1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EP1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EQ1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="ER1" s="1" t="inlineStr">
-        <is>
-          <t>dividendDate</t>
-        </is>
-      </c>
-      <c r="ES1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="ET1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EU1" s="1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EV1" s="1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EW1" s="1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EX1" s="1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EY1" s="1" t="inlineStr">
-        <is>
-          <t>averageAnalystRating</t>
-        </is>
-      </c>
-      <c r="EZ1" s="1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="FA1" s="1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="FB1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="FC1" s="1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="FD1" s="1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="FE1" s="1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="FF1" s="1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="FG1" s="1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="FH1" s="1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="FI1" s="1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="FJ1" s="1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="FK1" s="1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="FL1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="FM1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="FN1" s="1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="FO1" s="1" t="inlineStr">
+      <c r="FS1" s="1" t="inlineStr">
         <is>
           <t>displayName</t>
         </is>
       </c>
-      <c r="FP1" s="1" t="inlineStr">
+      <c r="FT1" s="1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -1382,34 +1402,34 @@
         <v>2</v>
       </c>
       <c r="V2" t="n">
-        <v>63.57</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="W2" t="n">
-        <v>64</v>
+        <v>64.97</v>
       </c>
       <c r="X2" t="n">
-        <v>63.62</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="Y2" t="n">
-        <v>64.20999999999999</v>
+        <v>65.145</v>
       </c>
       <c r="Z2" t="n">
-        <v>63.57</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="AA2" t="n">
-        <v>64</v>
+        <v>64.97</v>
       </c>
       <c r="AB2" t="n">
-        <v>63.62</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>64.20999999999999</v>
+        <v>65.145</v>
       </c>
       <c r="AD2" t="n">
         <v>3.73</v>
       </c>
       <c r="AE2" t="n">
-        <v>5.87</v>
+        <v>5.76</v>
       </c>
       <c r="AF2" t="n">
         <v>1755216000</v>
@@ -1424,40 +1444,40 @@
         <v>0.626</v>
       </c>
       <c r="AJ2" t="n">
-        <v>10.213375</v>
+        <v>10.318472</v>
       </c>
       <c r="AK2" t="n">
-        <v>9.404692000000001</v>
+        <v>9.501467</v>
       </c>
       <c r="AL2" t="n">
-        <v>2068530</v>
+        <v>6322263</v>
       </c>
       <c r="AM2" t="n">
-        <v>2068530</v>
+        <v>6322263</v>
       </c>
       <c r="AN2" t="n">
-        <v>3390238</v>
+        <v>3454763</v>
       </c>
       <c r="AO2" t="n">
-        <v>3319090</v>
+        <v>3800580</v>
       </c>
       <c r="AP2" t="n">
-        <v>3319090</v>
+        <v>3800580</v>
       </c>
       <c r="AQ2" t="n">
-        <v>64.12</v>
+        <v>64.73</v>
       </c>
       <c r="AR2" t="n">
-        <v>64.11</v>
+        <v>64.75</v>
       </c>
       <c r="AS2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AT2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AU2" t="n">
-        <v>103591075840</v>
+        <v>107447992320</v>
       </c>
       <c r="AV2" t="n">
         <v>51.67</v>
@@ -1472,19 +1492,19 @@
         <v>7.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.9280291</v>
+        <v>1.9998137</v>
       </c>
       <c r="BA2" t="n">
-        <v>61.956</v>
+        <v>62.2736</v>
       </c>
       <c r="BB2" t="n">
-        <v>60.74325</v>
+        <v>60.76865</v>
       </c>
       <c r="BC2" t="n">
         <v>3.73</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.058675475</v>
+        <v>0.057007488</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1495,7 +1515,7 @@
         <v>0</v>
       </c>
       <c r="BG2" t="n">
-        <v>121294962688</v>
+        <v>123292237824</v>
       </c>
       <c r="BH2" t="n">
         <v>0.19118</v>
@@ -1507,40 +1527,40 @@
         <v>1253877361</v>
       </c>
       <c r="BK2" t="n">
-        <v>8258729</v>
+        <v>6337556</v>
       </c>
       <c r="BL2" t="n">
-        <v>9346828</v>
+        <v>8468005</v>
       </c>
       <c r="BM2" t="n">
-        <v>1753920000</v>
+        <v>1755216000</v>
       </c>
       <c r="BN2" t="n">
-        <v>1756425600</v>
+        <v>1757894400</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.0050999997</v>
+        <v>0.0039</v>
       </c>
       <c r="BP2" t="n">
         <v>4.0000003e-05</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.098979995</v>
+        <v>0.09898999999999999</v>
       </c>
       <c r="BR2" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.0077</v>
+        <v>0.0058999998</v>
       </c>
       <c r="BT2" t="n">
-        <v>1639272520</v>
+        <v>1658148030</v>
       </c>
       <c r="BU2" t="n">
         <v>35.844</v>
       </c>
       <c r="BV2" t="n">
-        <v>1.7894207</v>
+        <v>1.8078339</v>
       </c>
       <c r="BW2" t="n">
         <v>1735603200</v>
@@ -1572,16 +1592,16 @@
         <v>1272585600</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.258</v>
+        <v>2.295</v>
       </c>
       <c r="CG2" t="n">
-        <v>6.662</v>
+        <v>6.771</v>
       </c>
       <c r="CH2" t="n">
-        <v>-0.06058812</v>
+        <v>-0.089504</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.16333759</v>
+        <v>0.1529237</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.48</v>
@@ -1595,7 +1615,7 @@
         </is>
       </c>
       <c r="CM2" t="n">
-        <v>64.14</v>
+        <v>64.8</v>
       </c>
       <c r="CN2" t="n">
         <v>91</v>
@@ -1715,173 +1735,185 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="DV2" t="n">
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="DW2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DX2" t="n">
+        <v>1758930211</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>1758916802</v>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>NYQ</t>
+        </is>
+      </c>
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>finmb_299199</t>
+        </is>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>America/New_York</t>
+        </is>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>EDT</t>
+        </is>
+      </c>
+      <c r="ED2" t="n">
+        <v>-14400000</v>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>us_market</t>
+        </is>
+      </c>
+      <c r="EF2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>-0.962857</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>Rio Tinto Plc</t>
+        </is>
+      </c>
+      <c r="EJ2" t="inlineStr">
+        <is>
+          <t>Rio Tinto Group</t>
+        </is>
+      </c>
+      <c r="EK2" t="n">
+        <v>13.130005</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>0.25411275</v>
+      </c>
+      <c r="EM2" t="inlineStr">
+        <is>
+          <t>51.67 - 72.08</t>
+        </is>
+      </c>
+      <c r="EN2" t="n">
+        <v>-7.279999</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>-0.10099887</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>-8.9504</v>
+      </c>
+      <c r="EQ2" t="n">
+        <v>1758758400</v>
+      </c>
+      <c r="ER2" t="n">
         <v>1753905600</v>
       </c>
-      <c r="DW2" t="n">
+      <c r="ES2" t="n">
         <v>1753905600</v>
       </c>
-      <c r="DX2" t="n">
+      <c r="ET2" t="n">
         <v>1753905600</v>
       </c>
-      <c r="DY2" t="n">
+      <c r="EU2" t="n">
         <v>1753864200</v>
       </c>
-      <c r="DZ2" t="n">
+      <c r="EV2" t="n">
         <v>1753864200</v>
       </c>
-      <c r="EA2" t="b">
+      <c r="EW2" t="b">
         <v>0</v>
       </c>
-      <c r="EB2" t="n">
+      <c r="EX2" t="n">
         <v>6.28</v>
       </c>
-      <c r="EC2" t="n">
+      <c r="EY2" t="n">
         <v>6.82</v>
       </c>
-      <c r="ED2" t="n">
+      <c r="EZ2" t="n">
         <v>5.87242</v>
       </c>
-      <c r="EE2" t="n">
-        <v>10.922243</v>
-      </c>
-      <c r="EF2" t="b">
+      <c r="FA2" t="n">
+        <v>11.034634</v>
+      </c>
+      <c r="FB2" t="n">
+        <v>2.5264015</v>
+      </c>
+      <c r="FC2" t="n">
+        <v>0.040569384</v>
+      </c>
+      <c r="FD2" t="n">
+        <v>4.031353</v>
+      </c>
+      <c r="FE2" t="n">
+        <v>0.06633935000000001</v>
+      </c>
+      <c r="FF2" t="n">
+        <v>15</v>
+      </c>
+      <c r="FG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH2" t="inlineStr">
+        <is>
+          <t>1.8 - Buy</t>
+        </is>
+      </c>
+      <c r="FI2" t="b">
+        <v>0</v>
+      </c>
+      <c r="FJ2" t="b">
         <v>1</v>
       </c>
-      <c r="EG2" t="n">
+      <c r="FK2" t="n">
         <v>646579800000</v>
       </c>
-      <c r="EH2" t="n">
-        <v>0.5699997</v>
-      </c>
-      <c r="EI2" t="inlineStr">
-        <is>
-          <t>63.62 - 64.21</t>
-        </is>
-      </c>
-      <c r="EJ2" t="inlineStr">
+      <c r="FL2" t="n">
+        <v>-0.7716049</v>
+      </c>
+      <c r="FM2" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="FN2" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="FO2" t="n">
+        <v>-0.629997</v>
+      </c>
+      <c r="FP2" t="inlineStr">
+        <is>
+          <t>64.43 - 65.145</t>
+        </is>
+      </c>
+      <c r="FQ2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="EK2" t="n">
-        <v>3390238</v>
-      </c>
-      <c r="EL2" t="n">
-        <v>12.470001</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>0.2413393</v>
-      </c>
-      <c r="EN2" t="inlineStr">
-        <is>
-          <t>51.67 - 72.08</t>
-        </is>
-      </c>
-      <c r="EO2" t="n">
-        <v>-7.9400024</v>
-      </c>
-      <c r="EP2" t="n">
-        <v>-0.11015541</v>
-      </c>
-      <c r="EQ2" t="n">
-        <v>-6.058812</v>
-      </c>
-      <c r="ER2" t="n">
-        <v>1758758400</v>
-      </c>
-      <c r="ES2" t="n">
-        <v>2.183998</v>
-      </c>
-      <c r="ET2" t="n">
-        <v>0.03525079</v>
-      </c>
-      <c r="EU2" t="n">
-        <v>3.3967476</v>
-      </c>
-      <c r="EV2" t="n">
-        <v>0.05591975</v>
-      </c>
-      <c r="EW2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EY2" t="inlineStr">
-        <is>
-          <t>1.8 - Buy</t>
-        </is>
-      </c>
-      <c r="EZ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="FA2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="FB2" t="n">
-        <v>1758740031</v>
-      </c>
-      <c r="FC2" t="inlineStr">
-        <is>
-          <t>Rio Tinto Plc</t>
-        </is>
-      </c>
-      <c r="FD2" t="inlineStr">
-        <is>
-          <t>Rio Tinto Group</t>
-        </is>
-      </c>
-      <c r="FE2" t="inlineStr">
-        <is>
-          <t>NYQ</t>
-        </is>
-      </c>
-      <c r="FF2" t="inlineStr">
-        <is>
-          <t>finmb_299199</t>
-        </is>
-      </c>
-      <c r="FG2" t="inlineStr">
-        <is>
-          <t>America/New_York</t>
-        </is>
-      </c>
-      <c r="FH2" t="inlineStr">
-        <is>
-          <t>EDT</t>
-        </is>
-      </c>
-      <c r="FI2" t="n">
-        <v>-14400000</v>
-      </c>
-      <c r="FJ2" t="inlineStr">
-        <is>
-          <t>us_market</t>
-        </is>
-      </c>
-      <c r="FK2" t="b">
-        <v>0</v>
-      </c>
-      <c r="FL2" t="n">
-        <v>0.89643735</v>
-      </c>
-      <c r="FM2" t="n">
-        <v>64.14</v>
-      </c>
-      <c r="FN2" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="FO2" t="inlineStr">
+      <c r="FR2" t="n">
+        <v>3454763</v>
+      </c>
+      <c r="FS2" t="inlineStr">
         <is>
           <t>Rio Tinto</t>
         </is>
       </c>
-      <c r="FP2" t="inlineStr"/>
+      <c r="FT2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
